--- a/12.xlsx
+++ b/12.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiros-h/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiros-h/Documents/【連載】デジタルアドバンテージ/12回/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90930E66-5463-694E-88D8-EB8F998B960D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E00EC6-E0DC-E74D-A9C1-6E84CE8B7EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12240" yWindow="6400" windowWidth="27500" windowHeight="16360" xr2:uid="{F9528CDD-3F2A-9C45-AB3E-4F6C69C8217C}"/>
+    <workbookView xWindow="1120" yWindow="600" windowWidth="50080" windowHeight="28200" activeTab="1" xr2:uid="{F9528CDD-3F2A-9C45-AB3E-4F6C69C8217C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="18">
   <si>
     <t>収益力</t>
   </si>
@@ -71,12 +72,58 @@
     <t>リターン</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>収益力</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">シュウエキリョク </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>成長性</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">セイチョウセイ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>割安性</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ワリヤスセイ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>業種</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>金融</t>
+  </si>
+  <si>
+    <t>小売</t>
+  </si>
+  <si>
+    <t>製造業</t>
+  </si>
+  <si>
+    <t>不動産</t>
+  </si>
+  <si>
+    <t>番号</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">バンゴウ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -105,6 +152,15 @@
       <color theme="1"/>
       <name val="游ゴシック Regular"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -155,7 +211,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -166,6 +222,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1835,4 +1897,1035 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB2FB1A-DAB0-2D4B-846F-CB0D77759986}">
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D2">
+        <v>23.9</v>
+      </c>
+      <c r="E2">
+        <v>0.93</v>
+      </c>
+      <c r="F2">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>12.2</v>
+      </c>
+      <c r="D3">
+        <v>-4</v>
+      </c>
+      <c r="E3">
+        <v>0.46</v>
+      </c>
+      <c r="F3">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>18.8</v>
+      </c>
+      <c r="D4">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E4">
+        <v>0.54</v>
+      </c>
+      <c r="F4">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>12.5</v>
+      </c>
+      <c r="D5">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.35</v>
+      </c>
+      <c r="F5">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>15.7</v>
+      </c>
+      <c r="D6">
+        <v>23.1</v>
+      </c>
+      <c r="E6">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F6">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D7">
+        <v>14.5</v>
+      </c>
+      <c r="E7">
+        <v>0.35</v>
+      </c>
+      <c r="F7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>13.3</v>
+      </c>
+      <c r="D8">
+        <v>17.3</v>
+      </c>
+      <c r="E8">
+        <v>0.65</v>
+      </c>
+      <c r="F8">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>17.2</v>
+      </c>
+      <c r="E9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F9">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>15.6</v>
+      </c>
+      <c r="D10">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.69</v>
+      </c>
+      <c r="F10">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D11">
+        <v>10.3</v>
+      </c>
+      <c r="E11">
+        <v>0.36</v>
+      </c>
+      <c r="F11">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>11.1</v>
+      </c>
+      <c r="D12">
+        <v>12.2</v>
+      </c>
+      <c r="E12">
+        <v>1.22</v>
+      </c>
+      <c r="F12">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>11.6</v>
+      </c>
+      <c r="D13">
+        <v>-0.9</v>
+      </c>
+      <c r="E13">
+        <v>0.98</v>
+      </c>
+      <c r="F13">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>7.2</v>
+      </c>
+      <c r="D14">
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>15.6</v>
+      </c>
+      <c r="D15">
+        <v>9.9</v>
+      </c>
+      <c r="E15">
+        <v>1.04</v>
+      </c>
+      <c r="F15">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>11.6</v>
+      </c>
+      <c r="D16">
+        <v>2.1</v>
+      </c>
+      <c r="E16">
+        <v>1.32</v>
+      </c>
+      <c r="F16">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>13.5</v>
+      </c>
+      <c r="D17">
+        <v>3.1</v>
+      </c>
+      <c r="E17">
+        <v>1.01</v>
+      </c>
+      <c r="F17">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>6.7</v>
+      </c>
+      <c r="D18">
+        <v>1.6</v>
+      </c>
+      <c r="E18">
+        <v>1.42</v>
+      </c>
+      <c r="F18">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>11.4</v>
+      </c>
+      <c r="D19">
+        <v>14.4</v>
+      </c>
+      <c r="E19">
+        <v>1.39</v>
+      </c>
+      <c r="F19">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D20">
+        <v>12.2</v>
+      </c>
+      <c r="E20">
+        <v>1.22</v>
+      </c>
+      <c r="F20">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>7.4</v>
+      </c>
+      <c r="D21">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E21">
+        <v>0.88</v>
+      </c>
+      <c r="F21">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>7.1</v>
+      </c>
+      <c r="E22">
+        <v>0.97</v>
+      </c>
+      <c r="F22">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D23">
+        <v>3.7</v>
+      </c>
+      <c r="E23">
+        <v>0.82</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24">
+        <v>10.4</v>
+      </c>
+      <c r="D24">
+        <v>2.8</v>
+      </c>
+      <c r="E24">
+        <v>0.95</v>
+      </c>
+      <c r="F24">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>6.9</v>
+      </c>
+      <c r="D25">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E25">
+        <v>1.05</v>
+      </c>
+      <c r="F25">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>11.6</v>
+      </c>
+      <c r="E26">
+        <v>1.29</v>
+      </c>
+      <c r="F26">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>7.1</v>
+      </c>
+      <c r="D27">
+        <v>14.9</v>
+      </c>
+      <c r="E27">
+        <v>1.26</v>
+      </c>
+      <c r="F27">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>15.1</v>
+      </c>
+      <c r="D28">
+        <v>0.2</v>
+      </c>
+      <c r="E28">
+        <v>0.94</v>
+      </c>
+      <c r="F28">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>11.9</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>0.93</v>
+      </c>
+      <c r="F29">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <v>7.4</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>1.18</v>
+      </c>
+      <c r="F30">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>10.1</v>
+      </c>
+      <c r="D31">
+        <v>23</v>
+      </c>
+      <c r="E31">
+        <v>0.86</v>
+      </c>
+      <c r="F31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>16.2</v>
+      </c>
+      <c r="D32">
+        <v>-2.7</v>
+      </c>
+      <c r="E32">
+        <v>0.94</v>
+      </c>
+      <c r="F32">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D33">
+        <v>0.2</v>
+      </c>
+      <c r="E33">
+        <v>0.98</v>
+      </c>
+      <c r="F33">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>15.3</v>
+      </c>
+      <c r="D34">
+        <v>3.1</v>
+      </c>
+      <c r="E34">
+        <v>0.77</v>
+      </c>
+      <c r="F34">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35">
+        <v>18.3</v>
+      </c>
+      <c r="D35">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E35">
+        <v>0.64</v>
+      </c>
+      <c r="F35">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
+        <v>14.2</v>
+      </c>
+      <c r="D36">
+        <v>4.3</v>
+      </c>
+      <c r="E36">
+        <v>0.95</v>
+      </c>
+      <c r="F36">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>6.1</v>
+      </c>
+      <c r="D37">
+        <v>5.9</v>
+      </c>
+      <c r="E37">
+        <v>0.5</v>
+      </c>
+      <c r="F37">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>12</v>
+      </c>
+      <c r="D38">
+        <v>11.8</v>
+      </c>
+      <c r="E38">
+        <v>1.02</v>
+      </c>
+      <c r="F38">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>8.9</v>
+      </c>
+      <c r="D39">
+        <v>13.3</v>
+      </c>
+      <c r="E39">
+        <v>0.95</v>
+      </c>
+      <c r="F39">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40">
+        <v>12.7</v>
+      </c>
+      <c r="D40">
+        <v>16.7</v>
+      </c>
+      <c r="E40">
+        <v>1.38</v>
+      </c>
+      <c r="F40">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>11.8</v>
+      </c>
+      <c r="D41">
+        <v>12.7</v>
+      </c>
+      <c r="E41">
+        <v>0.89</v>
+      </c>
+      <c r="F41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>8.6</v>
+      </c>
+      <c r="D42">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E42">
+        <v>1.03</v>
+      </c>
+      <c r="F42">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>11.7</v>
+      </c>
+      <c r="D43">
+        <v>6.5</v>
+      </c>
+      <c r="E43">
+        <v>1.59</v>
+      </c>
+      <c r="F43">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>15.8</v>
+      </c>
+      <c r="E44">
+        <v>1.03</v>
+      </c>
+      <c r="F44">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45">
+        <v>7.8</v>
+      </c>
+      <c r="D45">
+        <v>5.2</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <v>14</v>
+      </c>
+      <c r="D46">
+        <v>0.8</v>
+      </c>
+      <c r="E46">
+        <v>1.01</v>
+      </c>
+      <c r="F46">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47">
+        <v>11.5</v>
+      </c>
+      <c r="D47">
+        <v>-1.8</v>
+      </c>
+      <c r="E47">
+        <v>0.66</v>
+      </c>
+      <c r="F47">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48">
+        <v>11</v>
+      </c>
+      <c r="D48">
+        <v>-6.8</v>
+      </c>
+      <c r="E48">
+        <v>1.04</v>
+      </c>
+      <c r="F48">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49">
+        <v>13.9</v>
+      </c>
+      <c r="D49">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E49">
+        <v>1.28</v>
+      </c>
+      <c r="F49">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50">
+        <v>10.8</v>
+      </c>
+      <c r="D50">
+        <v>-0.4</v>
+      </c>
+      <c r="E50">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="F50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="5">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-0.8</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0.89</v>
+      </c>
+      <c r="F51" s="5">
+        <v>6.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/12.xlsx
+++ b/12.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiros-h/Documents/【連載】デジタルアドバンテージ/12回/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E00EC6-E0DC-E74D-A9C1-6E84CE8B7EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B540037E-8A04-5047-9D36-2E07D59195EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="600" windowWidth="50080" windowHeight="28200" activeTab="1" xr2:uid="{F9528CDD-3F2A-9C45-AB3E-4F6C69C8217C}"/>
+    <workbookView xWindow="20760" yWindow="600" windowWidth="50080" windowHeight="28200" activeTab="1" xr2:uid="{F9528CDD-3F2A-9C45-AB3E-4F6C69C8217C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="20">
   <si>
     <t>収益力</t>
   </si>
@@ -118,6 +119,47 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>株価ファンダメンタル分析データ（各種指標と翌年リターン）</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カブカ </t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t xml:space="preserve">ブンセキ </t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t xml:space="preserve">カクシュシヒョウ </t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t xml:space="preserve">ヨクネン </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>株価ファンダメンタル分析データ（各種指標と翌年リターン）：標準化・ダミー変数化済み</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カブカ </t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t xml:space="preserve">ブンセキ </t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t xml:space="preserve">カクシュシヒョウ </t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t xml:space="preserve">ヨクネン </t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t xml:space="preserve">ヒョウジュンカ </t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t xml:space="preserve">カ </t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t xml:space="preserve">スミ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -163,7 +205,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,6 +215,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -211,7 +259,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -228,6 +276,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -564,96 +618,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1146B275-E023-174D-A485-CE10604D6723}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2">
-        <v>0.35704080699561891</v>
-      </c>
-      <c r="B2" s="2">
-        <v>-1.28349513677482</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1.301359668043272</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2">
-        <v>-0.21802491855754791</v>
-      </c>
-      <c r="B3" s="2">
-        <v>5.5804136381513943E-2</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1.0551564876026529</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>18.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2">
-        <v>0.55706366805758956</v>
+        <v>0.35704080699561891</v>
       </c>
       <c r="B4" s="2">
-        <v>-1.395103409537847</v>
+        <v>-1.28349513677482</v>
       </c>
       <c r="C4" s="2">
-        <v>0.1758594146004423</v>
+        <v>1.301359668043272</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -668,18 +680,18 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2">
-        <v>0.75708652911956076</v>
+        <v>-0.21802491855754791</v>
       </c>
       <c r="B5" s="2">
-        <v>0.93471928439035745</v>
+        <v>5.5804136381513943E-2</v>
       </c>
       <c r="C5" s="2">
-        <v>-1.2310159022030951</v>
+        <v>1.0551564876026529</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -694,18 +706,18 @@
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>28.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2">
-        <v>-1.0431192204381781</v>
+        <v>0.55706366805758956</v>
       </c>
       <c r="B6" s="2">
-        <v>-1.7438792619223089</v>
+        <v>-1.395103409537847</v>
       </c>
       <c r="C6" s="2">
-        <v>-1.3717034338834491</v>
+        <v>0.1758594146004423</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -720,18 +732,18 @@
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2">
-        <v>-0.49305635251775792</v>
+        <v>0.75708652911956076</v>
       </c>
       <c r="B7" s="2">
-        <v>-0.64174756838740976</v>
+        <v>0.93471928439035745</v>
       </c>
       <c r="C7" s="2">
-        <v>-3.5171882920088458E-2</v>
+        <v>-1.2310159022030951</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -746,18 +758,18 @@
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>5</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2">
-        <v>0.70708081385406774</v>
+        <v>-1.0431192204381781</v>
       </c>
       <c r="B8" s="2">
-        <v>0.57199239791051726</v>
+        <v>-1.7438792619223089</v>
       </c>
       <c r="C8" s="2">
-        <v>0.1055156487602654</v>
+        <v>-1.3717034338834491</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -772,18 +784,18 @@
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>18.399999999999999</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2">
-        <v>1.782203692062162</v>
+        <v>-0.49305635251775792</v>
       </c>
       <c r="B9" s="2">
-        <v>1.799683398303823</v>
+        <v>-0.64174756838740976</v>
       </c>
       <c r="C9" s="2">
-        <v>0.84412519008212261</v>
+        <v>-3.5171882920088458E-2</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -798,18 +810,18 @@
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>25.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2">
-        <v>1.707195119163923</v>
+        <v>0.70708081385406774</v>
       </c>
       <c r="B10" s="2">
-        <v>1.981046841543743</v>
+        <v>0.57199239791051726</v>
       </c>
       <c r="C10" s="2">
-        <v>0.91446895592229882</v>
+        <v>0.1055156487602654</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -824,18 +836,18 @@
         <v>0</v>
       </c>
       <c r="H10" s="2">
-        <v>27.4</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2">
-        <v>1.5571779733674449</v>
+        <v>1.782203692062162</v>
       </c>
       <c r="B11" s="2">
-        <v>1.4230054777286041</v>
+        <v>1.799683398303823</v>
       </c>
       <c r="C11" s="2">
-        <v>1.4420471997236259</v>
+        <v>0.84412519008212261</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -847,21 +859,21 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2">
-        <v>23.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2">
-        <v>0.88210081728329259</v>
+        <v>1.707195119163923</v>
       </c>
       <c r="B12" s="2">
-        <v>1.08818065943952</v>
+        <v>1.981046841543743</v>
       </c>
       <c r="C12" s="2">
-        <v>-1.758594146004421</v>
+        <v>0.91446895592229882</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -873,21 +885,21 @@
         <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>10.6</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2">
-        <v>-1.6931935188895839</v>
+        <v>1.5571779733674449</v>
       </c>
       <c r="B13" s="2">
-        <v>0.51618826152900332</v>
+        <v>1.4230054777286041</v>
       </c>
       <c r="C13" s="2">
-        <v>0</v>
+        <v>1.4420471997236259</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -902,18 +914,18 @@
         <v>1</v>
       </c>
       <c r="H13" s="2">
-        <v>7.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2">
-        <v>-1.293147796765642</v>
+        <v>0.88210081728329259</v>
       </c>
       <c r="B14" s="2">
-        <v>-1.28349513677482</v>
+        <v>1.08818065943952</v>
       </c>
       <c r="C14" s="2">
-        <v>-1.195844019283006</v>
+        <v>-1.758594146004421</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
@@ -928,18 +940,18 @@
         <v>1</v>
       </c>
       <c r="H14" s="2">
-        <v>5.2</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2">
-        <v>1.5321751157346979</v>
+        <v>-1.6931935188895839</v>
       </c>
       <c r="B15" s="2">
-        <v>9.7657238667649193E-2</v>
+        <v>0.51618826152900332</v>
       </c>
       <c r="C15" s="2">
-        <v>0.94964083884238726</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
@@ -954,18 +966,18 @@
         <v>1</v>
       </c>
       <c r="H15" s="2">
-        <v>14.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2">
-        <v>-1.393159227296628</v>
+        <v>-1.293147796765642</v>
       </c>
       <c r="B16" s="2">
-        <v>0.47433515924286812</v>
+        <v>-1.28349513677482</v>
       </c>
       <c r="C16" s="2">
-        <v>-0.38689071212097259</v>
+        <v>-1.195844019283006</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -980,18 +992,18 @@
         <v>1</v>
       </c>
       <c r="H16" s="2">
-        <v>15.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2">
-        <v>0.1070122306681551</v>
+        <v>1.5321751157346979</v>
       </c>
       <c r="B17" s="2">
-        <v>4.1853102286135258E-2</v>
+        <v>9.7657238667649193E-2</v>
       </c>
       <c r="C17" s="2">
-        <v>-0.80895330716203384</v>
+        <v>0.94964083884238726</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -1006,18 +1018,18 @@
         <v>1</v>
       </c>
       <c r="H17" s="2">
-        <v>10.199999999999999</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2">
-        <v>-1.243142081500149</v>
+        <v>-1.393159227296628</v>
       </c>
       <c r="B18" s="2">
-        <v>-0.96262135258111448</v>
+        <v>0.47433515924286812</v>
       </c>
       <c r="C18" s="2">
-        <v>-1.090328370522742</v>
+        <v>-0.38689071212097259</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -1032,18 +1044,18 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>0.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2">
-        <v>0.88210081728329259</v>
+        <v>0.1070122306681551</v>
       </c>
       <c r="B19" s="2">
-        <v>0.79520894343657278</v>
+        <v>4.1853102286135258E-2</v>
       </c>
       <c r="C19" s="2">
-        <v>0.2110312975205304</v>
+        <v>-0.80895330716203384</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
@@ -1058,70 +1070,70 @@
         <v>1</v>
       </c>
       <c r="H19" s="2">
-        <v>15.9</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2">
-        <v>1.0571208207125169</v>
+        <v>-1.243142081500149</v>
       </c>
       <c r="B20" s="2">
-        <v>0.99052342077187139</v>
+        <v>-0.96262135258111448</v>
       </c>
       <c r="C20" s="2">
-        <v>0.38689071212097259</v>
+        <v>-1.090328370522742</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
       </c>
       <c r="G20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2">
-        <v>12.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2">
-        <v>-0.19302206092480159</v>
+        <v>0.88210081728329259</v>
       </c>
       <c r="B21" s="2">
-        <v>0.78125790934119432</v>
+        <v>0.79520894343657278</v>
       </c>
       <c r="C21" s="2">
-        <v>-0.63309389256159188</v>
+        <v>0.2110312975205304</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
       <c r="G21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2">
-        <v>15.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2">
-        <v>-1.16813350860191</v>
+        <v>1.0571208207125169</v>
       </c>
       <c r="B22" s="2">
-        <v>0.44643309105211099</v>
+        <v>0.99052342077187139</v>
       </c>
       <c r="C22" s="2">
-        <v>0.66826577548168031</v>
+        <v>0.38689071212097259</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -1136,18 +1148,18 @@
         <v>0</v>
       </c>
       <c r="H22" s="2">
-        <v>21.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2">
-        <v>-0.1680192032920553</v>
+        <v>-0.19302206092480159</v>
       </c>
       <c r="B23" s="2">
-        <v>-0.59989446610127439</v>
+        <v>0.78125790934119432</v>
       </c>
       <c r="C23" s="2">
-        <v>-1.5123909655638019</v>
+        <v>-0.63309389256159188</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -1162,18 +1174,18 @@
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2">
-        <v>0.50705795279209698</v>
+        <v>-1.16813350860191</v>
       </c>
       <c r="B24" s="2">
-        <v>-4.1853102286135507E-2</v>
+        <v>0.44643309105211099</v>
       </c>
       <c r="C24" s="2">
-        <v>2.0399692093651289</v>
+        <v>0.66826577548168031</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
@@ -1188,18 +1200,18 @@
         <v>0</v>
       </c>
       <c r="H24" s="2">
-        <v>9.1999999999999993</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2">
-        <v>0.98211224781427819</v>
+        <v>-0.1680192032920553</v>
       </c>
       <c r="B25" s="2">
-        <v>-0.69755170476892359</v>
+        <v>-0.59989446610127439</v>
       </c>
       <c r="C25" s="2">
-        <v>1.019984604682564</v>
+        <v>-1.5123909655638019</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
@@ -1214,18 +1226,18 @@
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <v>12.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2">
-        <v>0.30703509173012578</v>
+        <v>0.50705795279209698</v>
       </c>
       <c r="B26" s="2">
-        <v>1.0323765230580071</v>
+        <v>-4.1853102286135507E-2</v>
       </c>
       <c r="C26" s="2">
-        <v>-0.1758594146004423</v>
+        <v>2.0399692093651289</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -1240,18 +1252,18 @@
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>16.899999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2">
-        <v>-0.99311350517268537</v>
+        <v>0.98211224781427819</v>
       </c>
       <c r="B27" s="2">
-        <v>-0.78125790934119443</v>
+        <v>-0.69755170476892359</v>
       </c>
       <c r="C27" s="2">
-        <v>-0.94964083884238759</v>
+        <v>1.019984604682564</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -1266,18 +1278,18 @@
         <v>0</v>
       </c>
       <c r="H27" s="2">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2">
-        <v>1.082123678345263</v>
+        <v>0.30703509173012578</v>
       </c>
       <c r="B28" s="2">
-        <v>1.18583789810717</v>
+        <v>1.0323765230580071</v>
       </c>
       <c r="C28" s="2">
-        <v>0.31654694628079583</v>
+        <v>-0.1758594146004423</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -1292,18 +1304,18 @@
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <v>19.600000000000001</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2">
-        <v>0.60706938332308258</v>
+        <v>-0.99311350517268537</v>
       </c>
       <c r="B29" s="2">
-        <v>0.46038412514748939</v>
+        <v>-0.78125790934119443</v>
       </c>
       <c r="C29" s="2">
-        <v>-7.0343765840176917E-2</v>
+        <v>-0.94964083884238759</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -1318,18 +1330,18 @@
         <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>14.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2">
-        <v>-1.0681220780709251</v>
+        <v>1.082123678345263</v>
       </c>
       <c r="B30" s="2">
-        <v>-0.7254537729596805</v>
+        <v>1.18583789810717</v>
       </c>
       <c r="C30" s="2">
-        <v>-1.160672136362918</v>
+        <v>0.31654694628079583</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
@@ -1344,18 +1356,18 @@
         <v>0</v>
       </c>
       <c r="H30" s="2">
-        <v>1.8</v>
+        <v>19.600000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2">
-        <v>0.20702366119914031</v>
+        <v>0.60706938332308258</v>
       </c>
       <c r="B31" s="2">
-        <v>0.33482481828908328</v>
+        <v>0.46038412514748939</v>
       </c>
       <c r="C31" s="2">
-        <v>-0.31654694628079583</v>
+        <v>-7.0343765840176917E-2</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1370,70 +1382,70 @@
         <v>0</v>
       </c>
       <c r="H31" s="2">
-        <v>17.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2">
-        <v>1.282146539407234</v>
+        <v>-1.0681220780709251</v>
       </c>
       <c r="B32" s="2">
-        <v>0.90681721619960065</v>
+        <v>-0.7254537729596805</v>
       </c>
       <c r="C32" s="2">
-        <v>-1.195844019283006</v>
+        <v>-1.160672136362918</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="2">
-        <v>19.399999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2">
-        <v>-0.69307921357972913</v>
+        <v>0.20702366119914031</v>
       </c>
       <c r="B33" s="2">
-        <v>0.50223722743362487</v>
+        <v>0.33482481828908328</v>
       </c>
       <c r="C33" s="2">
-        <v>-7.0343765840176917E-2</v>
+        <v>-0.31654694628079583</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="2">
-        <v>9</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2">
-        <v>-0.54306206778325095</v>
+        <v>1.282146539407234</v>
       </c>
       <c r="B34" s="2">
-        <v>1.325348239060955</v>
+        <v>0.90681721619960065</v>
       </c>
       <c r="C34" s="2">
-        <v>-0.31654694628079583</v>
+        <v>-1.195844019283006</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1448,18 +1460,18 @@
         <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>18.8</v>
+        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2">
-        <v>1.082123678345263</v>
+        <v>-0.69307921357972913</v>
       </c>
       <c r="B35" s="2">
-        <v>-0.15346137504916321</v>
+        <v>0.50223722743362487</v>
       </c>
       <c r="C35" s="2">
-        <v>0.94964083884238726</v>
+        <v>-7.0343765840176917E-2</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1474,18 +1486,18 @@
         <v>0</v>
       </c>
       <c r="H35" s="2">
-        <v>11.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2">
-        <v>0.60706938332308258</v>
+        <v>-0.54306206778325095</v>
       </c>
       <c r="B36" s="2">
-        <v>1.7020261596361741</v>
+        <v>1.325348239060955</v>
       </c>
       <c r="C36" s="2">
-        <v>-0.77378142424194529</v>
+        <v>-0.31654694628079583</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
@@ -1500,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1508,10 +1520,10 @@
         <v>1.082123678345263</v>
       </c>
       <c r="B37" s="2">
-        <v>-1.632270989159281</v>
+        <v>-0.15346137504916321</v>
       </c>
       <c r="C37" s="2">
-        <v>1.301359668043272</v>
+        <v>0.94964083884238726</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
@@ -1526,18 +1538,18 @@
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>16.899999999999999</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2">
-        <v>-0.71808207121247536</v>
+        <v>0.60706938332308258</v>
       </c>
       <c r="B38" s="2">
-        <v>-0.30692275009832642</v>
+        <v>1.7020261596361741</v>
       </c>
       <c r="C38" s="2">
-        <v>-0.562750126721415</v>
+        <v>-0.77378142424194529</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -1552,18 +1564,18 @@
         <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>7.8</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2">
-        <v>-1.1181277933364171</v>
+        <v>1.082123678345263</v>
       </c>
       <c r="B39" s="2">
-        <v>-0.68360067067354513</v>
+        <v>-1.632270989159281</v>
       </c>
       <c r="C39" s="2">
-        <v>-1.0551564876026529</v>
+        <v>1.301359668043272</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -1578,18 +1590,18 @@
         <v>0</v>
       </c>
       <c r="H39" s="2">
-        <v>4.0999999999999996</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2">
-        <v>0.53206081042484332</v>
+        <v>-0.71808207121247536</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2790206819075694</v>
+        <v>-0.30692275009832642</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
+        <v>-0.562750126721415</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
@@ -1604,18 +1616,18 @@
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>13.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2">
-        <v>-1.393159227296628</v>
+        <v>-1.1181277933364171</v>
       </c>
       <c r="B41" s="2">
-        <v>-0.90681721619960065</v>
+        <v>-0.68360067067354513</v>
       </c>
       <c r="C41" s="2">
-        <v>-1.2661877851231831</v>
+        <v>-1.0551564876026529</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
@@ -1630,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="H41" s="2">
-        <v>-2.4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2">
-        <v>-6.8007772761069757E-2</v>
+        <v>0.53206081042484332</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1255593068584063</v>
+        <v>0.2790206819075694</v>
       </c>
       <c r="C42" s="2">
-        <v>-0.49240636088123813</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
@@ -1656,18 +1668,18 @@
         <v>0</v>
       </c>
       <c r="H42" s="2">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2">
-        <v>-0.21802491855754791</v>
+        <v>-1.393159227296628</v>
       </c>
       <c r="B43" s="2">
-        <v>-0.29297171600294802</v>
+        <v>-0.90681721619960065</v>
       </c>
       <c r="C43" s="2">
-        <v>-0.59792200964150344</v>
+        <v>-1.2661877851231831</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -1682,70 +1694,70 @@
         <v>0</v>
       </c>
       <c r="H43" s="2">
-        <v>6.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2">
-        <v>-1.6181849459913451</v>
+        <v>-6.8007772761069757E-2</v>
       </c>
       <c r="B44" s="2">
-        <v>-0.66964963657816667</v>
+        <v>0.1255593068584063</v>
       </c>
       <c r="C44" s="2">
-        <v>0.80895330716203417</v>
+        <v>-0.49240636088123813</v>
       </c>
       <c r="D44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
       </c>
       <c r="F44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="2">
-        <v>8.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2">
-        <v>0.80709224438505334</v>
+        <v>-0.21802491855754791</v>
       </c>
       <c r="B45" s="2">
-        <v>-1.0323765230580071</v>
+        <v>-0.29297171600294802</v>
       </c>
       <c r="C45" s="2">
-        <v>0.80895330716203417</v>
+        <v>-0.59792200964150344</v>
       </c>
       <c r="D45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="2">
-        <v>17.899999999999999</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2">
-        <v>-0.59306778304874352</v>
+        <v>-1.6181849459913451</v>
       </c>
       <c r="B46" s="2">
-        <v>-1.841536500589958</v>
+        <v>-0.66964963657816667</v>
       </c>
       <c r="C46" s="2">
-        <v>-0.21103129752053079</v>
+        <v>0.80895330716203417</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -1760,18 +1772,18 @@
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <v>-3.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2">
-        <v>-1.16813350860191</v>
+        <v>0.80709224438505334</v>
       </c>
       <c r="B47" s="2">
-        <v>1.395103409537847</v>
+        <v>-1.0323765230580071</v>
       </c>
       <c r="C47" s="2">
-        <v>-1.5123909655638019</v>
+        <v>0.80895330716203417</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
@@ -1786,18 +1798,18 @@
         <v>0</v>
       </c>
       <c r="H47" s="2">
-        <v>5.5</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2">
-        <v>-0.31803634908853351</v>
+        <v>-0.59306778304874352</v>
       </c>
       <c r="B48" s="2">
-        <v>-0.97657238667649293</v>
+        <v>-1.841536500589958</v>
       </c>
       <c r="C48" s="2">
-        <v>1.793766028924509</v>
+        <v>-0.21103129752053079</v>
       </c>
       <c r="D48" s="2">
         <v>1</v>
@@ -1812,18 +1824,18 @@
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>8.8000000000000007</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2">
-        <v>-0.7430849288452217</v>
+        <v>-1.16813350860191</v>
       </c>
       <c r="B49" s="2">
-        <v>-0.89286618210422219</v>
+        <v>1.395103409537847</v>
       </c>
       <c r="C49" s="2">
-        <v>2.0399692093651289</v>
+        <v>-1.5123909655638019</v>
       </c>
       <c r="D49" s="2">
         <v>1</v>
@@ -1838,58 +1850,110 @@
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2">
+        <v>-0.31803634908853351</v>
+      </c>
+      <c r="B50" s="2">
+        <v>-0.97657238667649293</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1.793766028924509</v>
+      </c>
+      <c r="D50" s="2">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2">
+        <v>-0.7430849288452217</v>
+      </c>
+      <c r="B51" s="2">
+        <v>-0.89286618210422219</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2.0399692093651289</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2">
         <v>-1.6181849459913451</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B52" s="2">
         <v>-0.66964963657816667</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C52" s="2">
         <v>0.80895330716203417</v>
       </c>
-      <c r="D50" s="2">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2">
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2">
         <v>8.9</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="3">
+    <row r="53" spans="1:8">
+      <c r="A53" s="3">
         <v>0.80709224438505334</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B53" s="3">
         <v>-1.0323765230580071</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C53" s="3">
         <v>0.80895330716203417</v>
       </c>
-      <c r="D51" s="3">
-        <v>1</v>
-      </c>
-      <c r="E51" s="3">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3">
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
         <v>17.899999999999999</v>
       </c>
     </row>
@@ -1900,11 +1964,1052 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB2FB1A-DAB0-2D4B-846F-CB0D77759986}">
-  <dimension ref="A1:F51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A288D4D-6E31-774F-B5B6-D92958786097}">
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:6">
+      <c r="A1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>12.8</v>
+      </c>
+      <c r="D4">
+        <v>-0.8</v>
+      </c>
+      <c r="E4">
+        <v>1.25</v>
+      </c>
+      <c r="F4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>10.5</v>
+      </c>
+      <c r="D5">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E5">
+        <v>1.18</v>
+      </c>
+      <c r="F5">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>13.6</v>
+      </c>
+      <c r="D6">
+        <v>-1.6</v>
+      </c>
+      <c r="E6">
+        <v>0.93</v>
+      </c>
+      <c r="F6">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>14.4</v>
+      </c>
+      <c r="D7">
+        <v>15.1</v>
+      </c>
+      <c r="E7">
+        <v>0.53</v>
+      </c>
+      <c r="F7">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>7.2</v>
+      </c>
+      <c r="D8">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="E8">
+        <v>0.49</v>
+      </c>
+      <c r="F8">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>9.4</v>
+      </c>
+      <c r="D9">
+        <v>3.8</v>
+      </c>
+      <c r="E9">
+        <v>0.87</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>14.2</v>
+      </c>
+      <c r="D10">
+        <v>12.5</v>
+      </c>
+      <c r="E10">
+        <v>0.91</v>
+      </c>
+      <c r="F10">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>18.5</v>
+      </c>
+      <c r="D11">
+        <v>21.3</v>
+      </c>
+      <c r="E11">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F11">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>18.2</v>
+      </c>
+      <c r="D12">
+        <v>22.6</v>
+      </c>
+      <c r="E12">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="F12">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D13">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E13">
+        <v>1.29</v>
+      </c>
+      <c r="F13">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>14.9</v>
+      </c>
+      <c r="D14">
+        <v>16.2</v>
+      </c>
+      <c r="E14">
+        <v>0.38</v>
+      </c>
+      <c r="F14">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D15">
+        <v>12.1</v>
+      </c>
+      <c r="E15">
+        <v>0.88</v>
+      </c>
+      <c r="F15">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>6.2</v>
+      </c>
+      <c r="D16">
+        <v>-0.8</v>
+      </c>
+      <c r="E16">
+        <v>0.54</v>
+      </c>
+      <c r="F16">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>17.5</v>
+      </c>
+      <c r="D17">
+        <v>9.1</v>
+      </c>
+      <c r="E17">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F17">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>5.8</v>
+      </c>
+      <c r="D18">
+        <v>11.8</v>
+      </c>
+      <c r="E18">
+        <v>0.77</v>
+      </c>
+      <c r="F18">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>11.8</v>
+      </c>
+      <c r="D19">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E19">
+        <v>0.65</v>
+      </c>
+      <c r="F19">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>6.4</v>
+      </c>
+      <c r="D20">
+        <v>1.5</v>
+      </c>
+      <c r="E20">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F20">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>14.9</v>
+      </c>
+      <c r="D21">
+        <v>14.1</v>
+      </c>
+      <c r="E21">
+        <v>0.94</v>
+      </c>
+      <c r="F21">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>15.6</v>
+      </c>
+      <c r="D22">
+        <v>15.5</v>
+      </c>
+      <c r="E22">
+        <v>0.99</v>
+      </c>
+      <c r="F22">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <v>10.6</v>
+      </c>
+      <c r="D23">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>0.7</v>
+      </c>
+      <c r="F23">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24">
+        <v>6.7</v>
+      </c>
+      <c r="D24">
+        <v>11.6</v>
+      </c>
+      <c r="E24">
+        <v>1.07</v>
+      </c>
+      <c r="F24">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>10.7</v>
+      </c>
+      <c r="D25">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E25">
+        <v>0.45</v>
+      </c>
+      <c r="F25">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>13.4</v>
+      </c>
+      <c r="D26">
+        <v>8.1</v>
+      </c>
+      <c r="E26">
+        <v>1.46</v>
+      </c>
+      <c r="F26">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>15.3</v>
+      </c>
+      <c r="D27">
+        <v>3.4</v>
+      </c>
+      <c r="E27">
+        <v>1.17</v>
+      </c>
+      <c r="F27">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>12.6</v>
+      </c>
+      <c r="D28">
+        <v>15.8</v>
+      </c>
+      <c r="E28">
+        <v>0.83</v>
+      </c>
+      <c r="F28">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>7.4</v>
+      </c>
+      <c r="D29">
+        <v>2.8</v>
+      </c>
+      <c r="E29">
+        <v>0.61</v>
+      </c>
+      <c r="F29">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <v>15.7</v>
+      </c>
+      <c r="D30">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E30">
+        <v>0.97</v>
+      </c>
+      <c r="F30">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>13.8</v>
+      </c>
+      <c r="D31">
+        <v>11.7</v>
+      </c>
+      <c r="E31">
+        <v>0.86</v>
+      </c>
+      <c r="F31">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32">
+        <v>7.1</v>
+      </c>
+      <c r="D32">
+        <v>3.2</v>
+      </c>
+      <c r="E32">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F32">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>12.2</v>
+      </c>
+      <c r="D33">
+        <v>10.8</v>
+      </c>
+      <c r="E33">
+        <v>0.79</v>
+      </c>
+      <c r="F33">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>16.5</v>
+      </c>
+      <c r="D34">
+        <v>14.9</v>
+      </c>
+      <c r="E34">
+        <v>0.54</v>
+      </c>
+      <c r="F34">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35">
+        <v>8.6</v>
+      </c>
+      <c r="D35">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>0.86</v>
+      </c>
+      <c r="F35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D36">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="E36">
+        <v>0.79</v>
+      </c>
+      <c r="F36">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>15.7</v>
+      </c>
+      <c r="D37">
+        <v>7.3</v>
+      </c>
+      <c r="E37">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F37">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>13.8</v>
+      </c>
+      <c r="D38">
+        <v>20.6</v>
+      </c>
+      <c r="E38">
+        <v>0.66</v>
+      </c>
+      <c r="F38">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>15.7</v>
+      </c>
+      <c r="D39">
+        <v>-3.3</v>
+      </c>
+      <c r="E39">
+        <v>1.25</v>
+      </c>
+      <c r="F39">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40">
+        <v>8.5</v>
+      </c>
+      <c r="D40">
+        <v>6.2</v>
+      </c>
+      <c r="E40">
+        <v>0.72</v>
+      </c>
+      <c r="F40">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>6.9</v>
+      </c>
+      <c r="D41">
+        <v>3.5</v>
+      </c>
+      <c r="E41">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F41">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <v>13.5</v>
+      </c>
+      <c r="D42">
+        <v>10.4</v>
+      </c>
+      <c r="E42">
+        <v>0.88</v>
+      </c>
+      <c r="F42">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43">
+        <v>5.8</v>
+      </c>
+      <c r="D43">
+        <v>1.9</v>
+      </c>
+      <c r="E43">
+        <v>0.52</v>
+      </c>
+      <c r="F43">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <v>11.1</v>
+      </c>
+      <c r="D44">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E44">
+        <v>0.74</v>
+      </c>
+      <c r="F44">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45">
+        <v>10.5</v>
+      </c>
+      <c r="D45">
+        <v>6.3</v>
+      </c>
+      <c r="E45">
+        <v>0.71</v>
+      </c>
+      <c r="F45">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D46">
+        <v>3.6</v>
+      </c>
+      <c r="E46">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="F46">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47">
+        <v>14.6</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="F47">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48">
+        <v>9</v>
+      </c>
+      <c r="D48">
+        <v>-4.8</v>
+      </c>
+      <c r="E48">
+        <v>0.82</v>
+      </c>
+      <c r="F48">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49">
+        <v>6.7</v>
+      </c>
+      <c r="D49">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E49">
+        <v>0.45</v>
+      </c>
+      <c r="F49">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50">
+        <v>10.1</v>
+      </c>
+      <c r="D50">
+        <v>1.4</v>
+      </c>
+      <c r="E50">
+        <v>1.39</v>
+      </c>
+      <c r="F50">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51">
+        <v>8.4</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51">
+        <v>1.46</v>
+      </c>
+      <c r="F51">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D52">
+        <v>3.6</v>
+      </c>
+      <c r="E52">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="F52">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="5">
+        <v>50</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="D53" s="5">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="F53" s="5">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB2FB1A-DAB0-2D4B-846F-CB0D77759986}">
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
@@ -1924,7 +3029,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1943,8 +3048,24 @@
       <c r="F2">
         <v>19.399999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="H2">
+        <f>_xlfn.STDEV.P(C2:C51)</f>
+        <v>3.498904971558964</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2:K2" si="0">_xlfn.STDEV.P(D2:D51)</f>
+        <v>7.8442644014591991</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>0.28760778848981056</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>5.0472075447716671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1964,7 +3085,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1984,7 +3105,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2004,7 +3125,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2024,7 +3145,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2044,7 +3165,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2064,7 +3185,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2084,7 +3205,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2104,7 +3225,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2124,7 +3245,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2144,7 +3265,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2164,7 +3285,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2184,7 +3305,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2204,7 +3325,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15</v>
       </c>

--- a/12.xlsx
+++ b/12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiros-h/Documents/【連載】デジタルアドバンテージ/12回/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B540037E-8A04-5047-9D36-2E07D59195EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5B8100-7552-8245-8031-A43ECBC7BBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20760" yWindow="600" windowWidth="50080" windowHeight="28200" activeTab="1" xr2:uid="{F9528CDD-3F2A-9C45-AB3E-4F6C69C8217C}"/>
+    <workbookView xWindow="1120" yWindow="600" windowWidth="50080" windowHeight="28200" activeTab="2" xr2:uid="{F9528CDD-3F2A-9C45-AB3E-4F6C69C8217C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="20">
   <si>
     <t>収益力</t>
   </si>
@@ -3006,1042 +3006,1036 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB2FB1A-DAB0-2D4B-846F-CB0D77759986}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D2">
-        <v>23.9</v>
-      </c>
-      <c r="E2">
-        <v>0.93</v>
-      </c>
-      <c r="F2">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="H2">
-        <f>_xlfn.STDEV.P(C2:C51)</f>
-        <v>3.498904971558964</v>
-      </c>
-      <c r="I2">
-        <f t="shared" ref="I2:K2" si="0">_xlfn.STDEV.P(D2:D51)</f>
-        <v>7.8442644014591991</v>
-      </c>
-      <c r="J2">
-        <f t="shared" si="0"/>
-        <v>0.28760778848981056</v>
-      </c>
-      <c r="K2">
-        <f t="shared" si="0"/>
-        <v>5.0472075447716671</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>12.2</v>
-      </c>
-      <c r="D3">
-        <v>-4</v>
-      </c>
-      <c r="E3">
-        <v>0.46</v>
-      </c>
-      <c r="F3">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:6">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4">
-        <v>18.8</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D4">
-        <v>8.3000000000000007</v>
+        <v>23.9</v>
       </c>
       <c r="E4">
-        <v>0.54</v>
+        <v>0.93</v>
       </c>
       <c r="F4">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="D5">
-        <v>10.199999999999999</v>
+        <v>-4</v>
       </c>
       <c r="E5">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="F5">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6">
+        <v>18.8</v>
+      </c>
+      <c r="D6">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E6">
+        <v>0.54</v>
+      </c>
+      <c r="F6">
         <v>15.7</v>
       </c>
-      <c r="D6">
-        <v>23.1</v>
-      </c>
-      <c r="E6">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="F6">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>17.899999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="D7">
-        <v>14.5</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E7">
         <v>0.35</v>
       </c>
       <c r="F7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="D8">
-        <v>17.3</v>
+        <v>23.1</v>
       </c>
       <c r="E8">
-        <v>0.65</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="F8">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D9">
-        <v>17.2</v>
+        <v>14.5</v>
       </c>
       <c r="E9">
-        <v>0.55000000000000004</v>
+        <v>0.35</v>
       </c>
       <c r="F9">
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="D10">
-        <v>20.399999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="E10">
-        <v>0.69</v>
+        <v>0.65</v>
       </c>
       <c r="F10">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>17.2</v>
+      </c>
+      <c r="E11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F11">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>15.6</v>
+      </c>
+      <c r="D12">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.69</v>
+      </c>
+      <c r="F12">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
         <v>19.100000000000001</v>
       </c>
-      <c r="D11">
+      <c r="D13">
         <v>10.3</v>
       </c>
-      <c r="E11">
+      <c r="E13">
         <v>0.36</v>
       </c>
-      <c r="F11">
+      <c r="F13">
         <v>10.9</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
+    <row r="14" spans="1:6">
+      <c r="A14">
         <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>11.1</v>
-      </c>
-      <c r="D12">
-        <v>12.2</v>
-      </c>
-      <c r="E12">
-        <v>1.22</v>
-      </c>
-      <c r="F12">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13">
-        <v>11.6</v>
-      </c>
-      <c r="D13">
-        <v>-0.9</v>
-      </c>
-      <c r="E13">
-        <v>0.98</v>
-      </c>
-      <c r="F13">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14">
-        <v>7.2</v>
+        <v>11.1</v>
       </c>
       <c r="D14">
-        <v>-5.0999999999999996</v>
+        <v>12.2</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="F14">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="D15">
-        <v>9.9</v>
+        <v>-0.9</v>
       </c>
       <c r="E15">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="F15">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16">
-        <v>11.6</v>
+        <v>7.2</v>
       </c>
       <c r="D16">
-        <v>2.1</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="E16">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17">
-        <v>13.5</v>
+        <v>15.6</v>
       </c>
       <c r="D17">
-        <v>3.1</v>
+        <v>9.9</v>
       </c>
       <c r="E17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="F17">
-        <v>10.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18">
-        <v>6.7</v>
+        <v>11.6</v>
       </c>
       <c r="D18">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="E18">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="F18">
-        <v>8.1999999999999993</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19">
-        <v>11.4</v>
+        <v>13.5</v>
       </c>
       <c r="D19">
-        <v>14.4</v>
+        <v>3.1</v>
       </c>
       <c r="E19">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="F19">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20">
-        <v>8.6999999999999993</v>
+        <v>6.7</v>
       </c>
       <c r="D20">
-        <v>12.2</v>
+        <v>1.6</v>
       </c>
       <c r="E20">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="F20">
-        <v>12.7</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21">
-        <v>7.4</v>
+        <v>11.4</v>
       </c>
       <c r="D21">
-        <v>16.600000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="E21">
-        <v>0.88</v>
+        <v>1.39</v>
       </c>
       <c r="F21">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D22">
-        <v>7.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22">
-        <v>0.97</v>
+        <v>1.22</v>
       </c>
       <c r="F22">
-        <v>5.9</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23">
-        <v>8.6999999999999993</v>
+        <v>7.4</v>
       </c>
       <c r="D23">
-        <v>3.7</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E23">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24">
-        <v>10.4</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="E24">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="F24">
-        <v>10.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
       </c>
       <c r="C25">
-        <v>6.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D25">
-        <v>17.100000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="E25">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="F25">
-        <v>11.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="D26">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="E26">
-        <v>1.29</v>
+        <v>0.95</v>
       </c>
       <c r="F26">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
       <c r="C27">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="D27">
-        <v>14.9</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="E27">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="F27">
-        <v>7.1</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
       <c r="C28">
-        <v>15.1</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>0.2</v>
+        <v>11.6</v>
       </c>
       <c r="E28">
-        <v>0.94</v>
+        <v>1.29</v>
       </c>
       <c r="F28">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29">
-        <v>11.9</v>
+        <v>7.1</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>14.9</v>
       </c>
       <c r="E29">
-        <v>0.93</v>
+        <v>1.26</v>
       </c>
       <c r="F29">
-        <v>19.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
       </c>
       <c r="C30">
-        <v>7.4</v>
+        <v>15.1</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E30">
-        <v>1.18</v>
+        <v>0.94</v>
       </c>
       <c r="F30">
-        <v>3.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
       </c>
       <c r="C31">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="D31">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="F31">
-        <v>16</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>16.2</v>
+        <v>7.4</v>
       </c>
       <c r="D32">
-        <v>-2.7</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0.94</v>
+        <v>1.18</v>
       </c>
       <c r="F32">
-        <v>16.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33">
-        <v>8.6999999999999993</v>
+        <v>10.1</v>
       </c>
       <c r="D33">
-        <v>0.2</v>
+        <v>23</v>
       </c>
       <c r="E33">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="F33">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="D34">
-        <v>3.1</v>
+        <v>-2.7</v>
       </c>
       <c r="E34">
-        <v>0.77</v>
+        <v>0.94</v>
       </c>
       <c r="F34">
-        <v>6.3</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
       </c>
       <c r="C35">
-        <v>18.3</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D35">
-        <v>16.600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E35">
-        <v>0.64</v>
+        <v>0.98</v>
       </c>
       <c r="F35">
-        <v>15.1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
       </c>
       <c r="C36">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="D36">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="E36">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="F36">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37">
-        <v>6.1</v>
+        <v>18.3</v>
       </c>
       <c r="D37">
-        <v>5.9</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E37">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="F37">
-        <v>2.7</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
       </c>
       <c r="C38">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="D38">
-        <v>11.8</v>
+        <v>4.3</v>
       </c>
       <c r="E38">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="F38">
-        <v>1.1000000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39">
-        <v>8.9</v>
+        <v>6.1</v>
       </c>
       <c r="D39">
-        <v>13.3</v>
+        <v>5.9</v>
       </c>
       <c r="E39">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="F39">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
         <v>15</v>
       </c>
       <c r="C40">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="D40">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="E40">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="F40">
-        <v>9.5</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
       </c>
       <c r="C41">
-        <v>11.8</v>
+        <v>8.9</v>
       </c>
       <c r="D41">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="E41">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="F41">
-        <v>14</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C42">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="D42">
-        <v>4.9000000000000004</v>
+        <v>16.7</v>
       </c>
       <c r="E42">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="F42">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="D43">
-        <v>6.5</v>
+        <v>12.7</v>
       </c>
       <c r="E43">
-        <v>1.59</v>
+        <v>0.89</v>
       </c>
       <c r="F43">
-        <v>7.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="D44">
-        <v>15.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E44">
         <v>1.03</v>
       </c>
       <c r="F44">
-        <v>14.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
         <v>16</v>
       </c>
       <c r="C45">
-        <v>7.8</v>
+        <v>11.7</v>
       </c>
       <c r="D45">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="F45">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D46">
-        <v>0.8</v>
+        <v>15.8</v>
       </c>
       <c r="E46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="F46">
-        <v>4.9000000000000004</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="D47">
-        <v>-1.8</v>
+        <v>5.2</v>
       </c>
       <c r="E47">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D48">
-        <v>-6.8</v>
+        <v>0.8</v>
       </c>
       <c r="E48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="F48">
-        <v>5.2</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="D49">
-        <v>8.6999999999999993</v>
+        <v>-1.8</v>
       </c>
       <c r="E49">
-        <v>1.28</v>
+        <v>0.66</v>
       </c>
       <c r="F49">
-        <v>13</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50">
+        <v>11</v>
+      </c>
+      <c r="D50">
+        <v>-6.8</v>
+      </c>
+      <c r="E50">
+        <v>1.04</v>
+      </c>
+      <c r="F50">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51">
+        <v>13.9</v>
+      </c>
+      <c r="D51">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E51">
+        <v>1.28</v>
+      </c>
+      <c r="F51">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52">
         <v>10.8</v>
       </c>
-      <c r="D50">
+      <c r="D52">
         <v>-0.4</v>
       </c>
-      <c r="E50">
+      <c r="E52">
         <v>1.1399999999999999</v>
       </c>
-      <c r="F50">
+      <c r="F52">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="5">
+    <row r="53" spans="1:6">
+      <c r="A53" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B53" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C53" s="5">
         <v>10.199999999999999</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D53" s="5">
         <v>-0.8</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E53" s="5">
         <v>0.89</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F53" s="5">
         <v>6.7</v>
       </c>
     </row>
